--- a/outputs_final/consensus_seriation/consensus_seriation.xlsx
+++ b/outputs_final/consensus_seriation/consensus_seriation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/vms-seriation/outputs_original/consensus_seriation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/vms-seriation/outputs_final/consensus_seriation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E8F210-6860-C54A-AF22-7F8911F25EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A113BD-3BFD-1447-B0FD-3B233A54D210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5240" yWindow="660" windowWidth="25000" windowHeight="17840" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
   </bookViews>
@@ -1234,22 +1234,22 @@
         <v>f2, f7</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H6,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H6,Sheet2!A:C,3,FALSE))</f>
-        <v>f2, f7</v>
+        <v>f49, f56</v>
       </c>
       <c r="J6">
         <f>VLOOKUP(H6,Sheet2!A:C,2,FALSE)</f>
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="K6">
         <f>VLOOKUP(H6,Sheet2!A:C,3,FALSE)</f>
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="Q6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 5&amp;2&amp;f2, f7&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 5&amp;25&amp;f49, f56&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R6" t="s">
         <v>45</v>
       </c>
       <c r="S6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 5&amp;f49, f56&amp;f49, f56&amp;f2, f7&amp;f2, f7\\</v>
+        <v xml:space="preserve">    \ 5&amp;f49, f56&amp;f49, f56&amp;f2, f7&amp;f49, f56\\</v>
       </c>
       <c r="W6" t="s">
         <v>103</v>
@@ -1303,22 +1303,22 @@
         <v>f49, f56</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H7,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H7,Sheet2!A:C,3,FALSE))</f>
-        <v>f49, f56</v>
+        <v>f20, f21</v>
       </c>
       <c r="J7">
         <f>VLOOKUP(H7,Sheet2!A:C,2,FALSE)</f>
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <f>VLOOKUP(H7,Sheet2!A:C,3,FALSE)</f>
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -1333,14 +1333,14 @@
       </c>
       <c r="Q7" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 6&amp;25&amp;f49, f56&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 6&amp;12&amp;f20, f21&amp;Herbal A1&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R7" t="s">
         <v>46</v>
       </c>
       <c r="S7" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 6&amp;f20, f21&amp;f20, f21&amp;f49, f56&amp;f49, f56\\</v>
+        <v xml:space="preserve">    \ 6&amp;f20, f21&amp;f20, f21&amp;f49, f56&amp;f20, f21\\</v>
       </c>
       <c r="W7" t="s">
         <v>104</v>
@@ -1372,19 +1372,19 @@
         <v>f20, f21</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.CONCAT("f",VLOOKUP(H8,Sheet2!A:C,2,FALSE),", f",VLOOKUP(H8,Sheet2!A:C,3,FALSE))</f>
-        <v>f20, f21</v>
+        <v>f2, f7</v>
       </c>
       <c r="J8">
         <f>VLOOKUP(H8,Sheet2!A:C,2,FALSE)</f>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <f>VLOOKUP(H8,Sheet2!A:C,3,FALSE)</f>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M8" t="s">
         <v>33</v>
@@ -1402,14 +1402,14 @@
       </c>
       <c r="Q8" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 7&amp;12&amp;f20, f21&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 7&amp;2&amp;f2, f7&amp;Herbal A2&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R8" t="s">
         <v>47</v>
       </c>
       <c r="S8" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    \ 7&amp;f28, f29&amp;f4, f5&amp;f20, f21&amp;f20, f21\\</v>
+        <v xml:space="preserve">    \ 7&amp;f28, f29&amp;f4, f5&amp;f20, f21&amp;f2, f7\\</v>
       </c>
       <c r="W8" t="s">
         <v>105</v>

--- a/outputs_final/consensus_seriation/consensus_seriation.xlsx
+++ b/outputs_final/consensus_seriation/consensus_seriation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelgreshko/Documents/vms-seriation/outputs_final/consensus_seriation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A113BD-3BFD-1447-B0FD-3B233A54D210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF60223-F441-2C45-8ACC-6A9D0F3D4438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5240" yWindow="660" windowWidth="25000" windowHeight="17840" xr2:uid="{F6E16D77-EDEB-9D4B-BCE5-349C8D2A843B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="154">
   <si>
     <t>rank</t>
   </si>
@@ -496,6 +496,9 @@
   </si>
   <si>
     <t>Herbal A4</t>
+  </si>
+  <si>
+    <t>Herbal A5</t>
   </si>
 </sst>
 </file>
@@ -1870,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="M15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -1885,7 +1888,7 @@
       </c>
       <c r="Q15" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 14&amp;6&amp;f10, f15&amp;Herbal A3&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 14&amp;6&amp;f10, f15&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R15" t="s">
         <v>54</v>
@@ -1939,7 +1942,7 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -1954,7 +1957,7 @@
       </c>
       <c r="Q16" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 15&amp;7&amp;f11, f14&amp;Herbal A3&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 15&amp;7&amp;f11, f14&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R16" t="s">
         <v>55</v>
@@ -2008,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -2023,7 +2026,7 @@
       </c>
       <c r="Q17" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 16&amp;8&amp;f13, f0&amp;Herbal A3&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 16&amp;8&amp;f13, f0&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R17" t="s">
         <v>56</v>
@@ -2077,7 +2080,7 @@
         <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -2092,7 +2095,7 @@
       </c>
       <c r="Q18" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 17&amp;10&amp;f18, f23&amp;Herbal A3&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 17&amp;10&amp;f18, f23&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R18" t="s">
         <v>57</v>
@@ -2146,7 +2149,7 @@
         <v>45</v>
       </c>
       <c r="M19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -2161,7 +2164,7 @@
       </c>
       <c r="Q19" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 18&amp;24&amp;f44, f45&amp;Herbal A3&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 18&amp;24&amp;f44, f45&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R19" t="s">
         <v>58</v>
@@ -2215,7 +2218,7 @@
         <v>24</v>
       </c>
       <c r="M20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -2230,7 +2233,7 @@
       </c>
       <c r="Q20" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 19&amp;9&amp;f17, f24&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 19&amp;9&amp;f17, f24&amp;Herbal A5&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R20" t="s">
         <v>59</v>
@@ -2284,7 +2287,7 @@
         <v>6</v>
       </c>
       <c r="M21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N21">
         <v>1</v>
@@ -2299,7 +2302,7 @@
       </c>
       <c r="Q21" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 20&amp;3&amp;f3, f6&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 20&amp;3&amp;f3, f6&amp;Herbal A5&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R21" t="s">
         <v>60</v>
@@ -2353,7 +2356,7 @@
         <v>53</v>
       </c>
       <c r="M22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -2368,7 +2371,7 @@
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 21&amp;28&amp;f52, f53&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 21&amp;28&amp;f52, f53&amp;Herbal A5&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R22" t="s">
         <v>61</v>
@@ -2422,7 +2425,7 @@
         <v>54</v>
       </c>
       <c r="M23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -2437,7 +2440,7 @@
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    \ 22&amp;27&amp;f51, f54&amp;Herbal A4&amp;A&amp;A&amp;1\\</v>
+        <v xml:space="preserve">    \ 22&amp;27&amp;f51, f54&amp;Herbal A5&amp;A&amp;A&amp;1\\</v>
       </c>
       <c r="R23" t="s">
         <v>62</v>
